--- a/test_questionnaires/GlobalBank_Vendor_Due_Diligence_2026.xlsx
+++ b/test_questionnaires/GlobalBank_Vendor_Due_Diligence_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,10 +28,21 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,18 +51,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003F51B5"/>
-        <bgColor rgb="003F51B5"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5FF"/>
-        <bgColor rgb="00F5F5FF"/>
+        <fgColor rgb="00F5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -59,20 +73,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,15 +487,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -461,207 +509,279 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" t="n">
+          <t>Response
+(Yes / No / Partial / N-A)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comments / Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Provide your most recent SOC 2 Type II report date and audit period.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Do you hold a current SOC 2 Type II certification? If yes, provide the audit period and a copy upon request.</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Are all production system logins protected by phishing-resistant MFA (FIDO2 or equivalent)?</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="n">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Are you compliant with ISO 27001? Provide your certificate number and expiry date.</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Where is customer data physically stored? List all geographic regions and cloud providers.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Do you have documented policies for handling and protecting Personally Identifiable Information (PII)?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>What sub-processors or fourth parties have access to customer data? Provide a current list.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="n">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Is all data processed on behalf of GlobalBank stored exclusively within agreed geographic regions?</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Describe your encryption key management practices including rotation frequency and HSM usage.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Do you use subprocessors to handle GlobalBank data? If yes, provide a complete list.</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>What is your process for revoking employee access upon termination?</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" t="n">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Are phishing-resistant MFA methods (e.g. FIDO2 hardware keys) required for privileged administrator access?</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>How frequently do you test your disaster recovery plan and what were the results of the last test?</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Do you enforce network segmentation between production environments and internal corporate networks?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Do you have a formal vendor risk management program for your own third-party suppliers?</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" t="n">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Is customer data logically isolated from data belonging to other clients in your multi-tenant architecture?</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>How do you protect against insider threats?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Do you have a dedicated information security team or a named CISO / Head of Security?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Describe your network segmentation architecture between production and non-production environments.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" t="n">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Have you suffered any material cybersecurity incidents in the past 24 months? If yes, describe the nature and resolution.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>What security training is mandatory for all employees? How often is it completed?</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Do you carry cyber liability insurance? If yes, provide coverage amount and insurer.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>How do you detect and respond to DDoS attacks?</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" t="n">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Is access to production databases restricted to named individuals with a documented business need?</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>What change management controls are in place before changes reach production?</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="3" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Do you have controls in place to prevent employees from exfiltrating customer data (e.g. DLP tools)?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Describe your approach to data minimization and privacy by design.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" t="n">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Is all third-party code and open-source software tracked via a Software Bill of Materials (SBOM)?</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Do you have a formal bug bounty or responsible disclosure program?</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="3" t="n">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Do you perform annual penetration tests conducted by an accredited third-party firm?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>What GDPR and CCPA compliance mechanisms do you have in place?</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" t="n">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Are penetration test findings tracked to remediation with defined SLAs based on severity?</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>How do you manage secrets, API keys, and credentials across your infrastructure?</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="3" t="n">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Do you have a formal Supplier Risk Management program for your own vendors and cloud providers?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Describe your container and cloud workload security controls.</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Can you provide a completed Cloud Security Alliance (CSA) CAIQ on request?</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>What is the notification timeline for customers in the event of a confirmed data breach involving their data?</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Do you support data deletion requests from customers in compliance with GDPR / applicable privacy laws?</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Are all system clocks synchronised to a trusted time source (NTP) for audit log integrity?</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Do you have controls that restrict privileged access to production environments outside business hours?</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
